--- a/dataset/lecture_3_output/PaDelPy_fp_output.xlsx
+++ b/dataset/lecture_3_output/PaDelPy_fp_output.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,4417 +429,4417 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>CAS</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>PubChem_CID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP0</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP2</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP3</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP4</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP5</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP6</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP7</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP8</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP9</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP10</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP11</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP12</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP13</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP14</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP15</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP16</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP17</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP18</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP19</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP20</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP21</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP22</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP23</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP24</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP25</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP26</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP27</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP28</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP29</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP30</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP31</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP32</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP33</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP34</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP35</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP36</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP37</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP38</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP39</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP40</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP41</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP42</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP43</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP44</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP45</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP46</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP47</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP48</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP49</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP50</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP51</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP52</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP53</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP54</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP55</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP56</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP57</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP58</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP59</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP60</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP61</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP62</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP63</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP64</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP65</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP66</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP67</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP68</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP69</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP70</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP71</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP72</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP73</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP74</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP75</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP76</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP77</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP78</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP79</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP80</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP81</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP82</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP83</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP84</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP85</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP86</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP87</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP88</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP89</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP90</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP91</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP92</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP93</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP94</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP95</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP96</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP97</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP98</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP99</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP100</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP101</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP102</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP103</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP104</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP105</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP106</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP107</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP108</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP109</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP110</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP111</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP112</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP113</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP114</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP115</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP116</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP117</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP118</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP119</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP120</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP121</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP122</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP123</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP124</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP125</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP126</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP127</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP128</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP129</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP130</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP131</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP132</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP133</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP134</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP135</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP136</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP137</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP138</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP139</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP140</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP141</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP142</t>
         </is>
       </c>
-      <c r="EP1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP143</t>
         </is>
       </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP144</t>
         </is>
       </c>
-      <c r="ER1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP145</t>
         </is>
       </c>
-      <c r="ES1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP146</t>
         </is>
       </c>
-      <c r="ET1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP147</t>
         </is>
       </c>
-      <c r="EU1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP148</t>
         </is>
       </c>
-      <c r="EV1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP149</t>
         </is>
       </c>
-      <c r="EW1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP150</t>
         </is>
       </c>
-      <c r="EX1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP151</t>
         </is>
       </c>
-      <c r="EY1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP152</t>
         </is>
       </c>
-      <c r="EZ1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP153</t>
         </is>
       </c>
-      <c r="FA1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP154</t>
         </is>
       </c>
-      <c r="FB1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP155</t>
         </is>
       </c>
-      <c r="FC1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP156</t>
         </is>
       </c>
-      <c r="FD1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP157</t>
         </is>
       </c>
-      <c r="FE1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP158</t>
         </is>
       </c>
-      <c r="FF1" t="inlineStr">
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP159</t>
         </is>
       </c>
-      <c r="FG1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP160</t>
         </is>
       </c>
-      <c r="FH1" t="inlineStr">
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP161</t>
         </is>
       </c>
-      <c r="FI1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP162</t>
         </is>
       </c>
-      <c r="FJ1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP163</t>
         </is>
       </c>
-      <c r="FK1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP164</t>
         </is>
       </c>
-      <c r="FL1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP165</t>
         </is>
       </c>
-      <c r="FM1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP166</t>
         </is>
       </c>
-      <c r="FN1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP167</t>
         </is>
       </c>
-      <c r="FO1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP168</t>
         </is>
       </c>
-      <c r="FP1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP169</t>
         </is>
       </c>
-      <c r="FQ1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP170</t>
         </is>
       </c>
-      <c r="FR1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP171</t>
         </is>
       </c>
-      <c r="FS1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP172</t>
         </is>
       </c>
-      <c r="FT1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP173</t>
         </is>
       </c>
-      <c r="FU1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP174</t>
         </is>
       </c>
-      <c r="FV1" t="inlineStr">
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP175</t>
         </is>
       </c>
-      <c r="FW1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP176</t>
         </is>
       </c>
-      <c r="FX1" t="inlineStr">
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP177</t>
         </is>
       </c>
-      <c r="FY1" t="inlineStr">
+      <c r="FY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP178</t>
         </is>
       </c>
-      <c r="FZ1" t="inlineStr">
+      <c r="FZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP179</t>
         </is>
       </c>
-      <c r="GA1" t="inlineStr">
+      <c r="GA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP180</t>
         </is>
       </c>
-      <c r="GB1" t="inlineStr">
+      <c r="GB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP181</t>
         </is>
       </c>
-      <c r="GC1" t="inlineStr">
+      <c r="GC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP182</t>
         </is>
       </c>
-      <c r="GD1" t="inlineStr">
+      <c r="GD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP183</t>
         </is>
       </c>
-      <c r="GE1" t="inlineStr">
+      <c r="GE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP184</t>
         </is>
       </c>
-      <c r="GF1" t="inlineStr">
+      <c r="GF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP185</t>
         </is>
       </c>
-      <c r="GG1" t="inlineStr">
+      <c r="GG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP186</t>
         </is>
       </c>
-      <c r="GH1" t="inlineStr">
+      <c r="GH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP187</t>
         </is>
       </c>
-      <c r="GI1" t="inlineStr">
+      <c r="GI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP188</t>
         </is>
       </c>
-      <c r="GJ1" t="inlineStr">
+      <c r="GJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP189</t>
         </is>
       </c>
-      <c r="GK1" t="inlineStr">
+      <c r="GK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP190</t>
         </is>
       </c>
-      <c r="GL1" t="inlineStr">
+      <c r="GL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP191</t>
         </is>
       </c>
-      <c r="GM1" t="inlineStr">
+      <c r="GM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP192</t>
         </is>
       </c>
-      <c r="GN1" t="inlineStr">
+      <c r="GN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP193</t>
         </is>
       </c>
-      <c r="GO1" t="inlineStr">
+      <c r="GO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP194</t>
         </is>
       </c>
-      <c r="GP1" t="inlineStr">
+      <c r="GP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP195</t>
         </is>
       </c>
-      <c r="GQ1" t="inlineStr">
+      <c r="GQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP196</t>
         </is>
       </c>
-      <c r="GR1" t="inlineStr">
+      <c r="GR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP197</t>
         </is>
       </c>
-      <c r="GS1" t="inlineStr">
+      <c r="GS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP198</t>
         </is>
       </c>
-      <c r="GT1" t="inlineStr">
+      <c r="GT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP199</t>
         </is>
       </c>
-      <c r="GU1" t="inlineStr">
+      <c r="GU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP200</t>
         </is>
       </c>
-      <c r="GV1" t="inlineStr">
+      <c r="GV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP201</t>
         </is>
       </c>
-      <c r="GW1" t="inlineStr">
+      <c r="GW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP202</t>
         </is>
       </c>
-      <c r="GX1" t="inlineStr">
+      <c r="GX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP203</t>
         </is>
       </c>
-      <c r="GY1" t="inlineStr">
+      <c r="GY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP204</t>
         </is>
       </c>
-      <c r="GZ1" t="inlineStr">
+      <c r="GZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP205</t>
         </is>
       </c>
-      <c r="HA1" t="inlineStr">
+      <c r="HA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP206</t>
         </is>
       </c>
-      <c r="HB1" t="inlineStr">
+      <c r="HB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP207</t>
         </is>
       </c>
-      <c r="HC1" t="inlineStr">
+      <c r="HC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP208</t>
         </is>
       </c>
-      <c r="HD1" t="inlineStr">
+      <c r="HD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP209</t>
         </is>
       </c>
-      <c r="HE1" t="inlineStr">
+      <c r="HE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP210</t>
         </is>
       </c>
-      <c r="HF1" t="inlineStr">
+      <c r="HF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP211</t>
         </is>
       </c>
-      <c r="HG1" t="inlineStr">
+      <c r="HG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP212</t>
         </is>
       </c>
-      <c r="HH1" t="inlineStr">
+      <c r="HH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP213</t>
         </is>
       </c>
-      <c r="HI1" t="inlineStr">
+      <c r="HI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP214</t>
         </is>
       </c>
-      <c r="HJ1" t="inlineStr">
+      <c r="HJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP215</t>
         </is>
       </c>
-      <c r="HK1" t="inlineStr">
+      <c r="HK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP216</t>
         </is>
       </c>
-      <c r="HL1" t="inlineStr">
+      <c r="HL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP217</t>
         </is>
       </c>
-      <c r="HM1" t="inlineStr">
+      <c r="HM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP218</t>
         </is>
       </c>
-      <c r="HN1" t="inlineStr">
+      <c r="HN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP219</t>
         </is>
       </c>
-      <c r="HO1" t="inlineStr">
+      <c r="HO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP220</t>
         </is>
       </c>
-      <c r="HP1" t="inlineStr">
+      <c r="HP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP221</t>
         </is>
       </c>
-      <c r="HQ1" t="inlineStr">
+      <c r="HQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP222</t>
         </is>
       </c>
-      <c r="HR1" t="inlineStr">
+      <c r="HR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP223</t>
         </is>
       </c>
-      <c r="HS1" t="inlineStr">
+      <c r="HS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP224</t>
         </is>
       </c>
-      <c r="HT1" t="inlineStr">
+      <c r="HT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP225</t>
         </is>
       </c>
-      <c r="HU1" t="inlineStr">
+      <c r="HU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP226</t>
         </is>
       </c>
-      <c r="HV1" t="inlineStr">
+      <c r="HV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP227</t>
         </is>
       </c>
-      <c r="HW1" t="inlineStr">
+      <c r="HW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP228</t>
         </is>
       </c>
-      <c r="HX1" t="inlineStr">
+      <c r="HX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP229</t>
         </is>
       </c>
-      <c r="HY1" t="inlineStr">
+      <c r="HY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP230</t>
         </is>
       </c>
-      <c r="HZ1" t="inlineStr">
+      <c r="HZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP231</t>
         </is>
       </c>
-      <c r="IA1" t="inlineStr">
+      <c r="IA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP232</t>
         </is>
       </c>
-      <c r="IB1" t="inlineStr">
+      <c r="IB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP233</t>
         </is>
       </c>
-      <c r="IC1" t="inlineStr">
+      <c r="IC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP234</t>
         </is>
       </c>
-      <c r="ID1" t="inlineStr">
+      <c r="ID1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP235</t>
         </is>
       </c>
-      <c r="IE1" t="inlineStr">
+      <c r="IE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP236</t>
         </is>
       </c>
-      <c r="IF1" t="inlineStr">
+      <c r="IF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP237</t>
         </is>
       </c>
-      <c r="IG1" t="inlineStr">
+      <c r="IG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP238</t>
         </is>
       </c>
-      <c r="IH1" t="inlineStr">
+      <c r="IH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP239</t>
         </is>
       </c>
-      <c r="II1" t="inlineStr">
+      <c r="II1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP240</t>
         </is>
       </c>
-      <c r="IJ1" t="inlineStr">
+      <c r="IJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP241</t>
         </is>
       </c>
-      <c r="IK1" t="inlineStr">
+      <c r="IK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP242</t>
         </is>
       </c>
-      <c r="IL1" t="inlineStr">
+      <c r="IL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP243</t>
         </is>
       </c>
-      <c r="IM1" t="inlineStr">
+      <c r="IM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP244</t>
         </is>
       </c>
-      <c r="IN1" t="inlineStr">
+      <c r="IN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP245</t>
         </is>
       </c>
-      <c r="IO1" t="inlineStr">
+      <c r="IO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP246</t>
         </is>
       </c>
-      <c r="IP1" t="inlineStr">
+      <c r="IP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP247</t>
         </is>
       </c>
-      <c r="IQ1" t="inlineStr">
+      <c r="IQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP248</t>
         </is>
       </c>
-      <c r="IR1" t="inlineStr">
+      <c r="IR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP249</t>
         </is>
       </c>
-      <c r="IS1" t="inlineStr">
+      <c r="IS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP250</t>
         </is>
       </c>
-      <c r="IT1" t="inlineStr">
+      <c r="IT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP251</t>
         </is>
       </c>
-      <c r="IU1" t="inlineStr">
+      <c r="IU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP252</t>
         </is>
       </c>
-      <c r="IV1" t="inlineStr">
+      <c r="IV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP253</t>
         </is>
       </c>
-      <c r="IW1" t="inlineStr">
+      <c r="IW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP254</t>
         </is>
       </c>
-      <c r="IX1" t="inlineStr">
+      <c r="IX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP255</t>
         </is>
       </c>
-      <c r="IY1" t="inlineStr">
+      <c r="IY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP256</t>
         </is>
       </c>
-      <c r="IZ1" t="inlineStr">
+      <c r="IZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP257</t>
         </is>
       </c>
-      <c r="JA1" t="inlineStr">
+      <c r="JA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP258</t>
         </is>
       </c>
-      <c r="JB1" t="inlineStr">
+      <c r="JB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP259</t>
         </is>
       </c>
-      <c r="JC1" t="inlineStr">
+      <c r="JC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP260</t>
         </is>
       </c>
-      <c r="JD1" t="inlineStr">
+      <c r="JD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP261</t>
         </is>
       </c>
-      <c r="JE1" t="inlineStr">
+      <c r="JE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP262</t>
         </is>
       </c>
-      <c r="JF1" t="inlineStr">
+      <c r="JF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP263</t>
         </is>
       </c>
-      <c r="JG1" t="inlineStr">
+      <c r="JG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP264</t>
         </is>
       </c>
-      <c r="JH1" t="inlineStr">
+      <c r="JH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP265</t>
         </is>
       </c>
-      <c r="JI1" t="inlineStr">
+      <c r="JI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP266</t>
         </is>
       </c>
-      <c r="JJ1" t="inlineStr">
+      <c r="JJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP267</t>
         </is>
       </c>
-      <c r="JK1" t="inlineStr">
+      <c r="JK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP268</t>
         </is>
       </c>
-      <c r="JL1" t="inlineStr">
+      <c r="JL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP269</t>
         </is>
       </c>
-      <c r="JM1" t="inlineStr">
+      <c r="JM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP270</t>
         </is>
       </c>
-      <c r="JN1" t="inlineStr">
+      <c r="JN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP271</t>
         </is>
       </c>
-      <c r="JO1" t="inlineStr">
+      <c r="JO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP272</t>
         </is>
       </c>
-      <c r="JP1" t="inlineStr">
+      <c r="JP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP273</t>
         </is>
       </c>
-      <c r="JQ1" t="inlineStr">
+      <c r="JQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP274</t>
         </is>
       </c>
-      <c r="JR1" t="inlineStr">
+      <c r="JR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP275</t>
         </is>
       </c>
-      <c r="JS1" t="inlineStr">
+      <c r="JS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP276</t>
         </is>
       </c>
-      <c r="JT1" t="inlineStr">
+      <c r="JT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP277</t>
         </is>
       </c>
-      <c r="JU1" t="inlineStr">
+      <c r="JU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP278</t>
         </is>
       </c>
-      <c r="JV1" t="inlineStr">
+      <c r="JV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP279</t>
         </is>
       </c>
-      <c r="JW1" t="inlineStr">
+      <c r="JW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP280</t>
         </is>
       </c>
-      <c r="JX1" t="inlineStr">
+      <c r="JX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP281</t>
         </is>
       </c>
-      <c r="JY1" t="inlineStr">
+      <c r="JY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP282</t>
         </is>
       </c>
-      <c r="JZ1" t="inlineStr">
+      <c r="JZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP283</t>
         </is>
       </c>
-      <c r="KA1" t="inlineStr">
+      <c r="KA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP284</t>
         </is>
       </c>
-      <c r="KB1" t="inlineStr">
+      <c r="KB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP285</t>
         </is>
       </c>
-      <c r="KC1" t="inlineStr">
+      <c r="KC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP286</t>
         </is>
       </c>
-      <c r="KD1" t="inlineStr">
+      <c r="KD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP287</t>
         </is>
       </c>
-      <c r="KE1" t="inlineStr">
+      <c r="KE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP288</t>
         </is>
       </c>
-      <c r="KF1" t="inlineStr">
+      <c r="KF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP289</t>
         </is>
       </c>
-      <c r="KG1" t="inlineStr">
+      <c r="KG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP290</t>
         </is>
       </c>
-      <c r="KH1" t="inlineStr">
+      <c r="KH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP291</t>
         </is>
       </c>
-      <c r="KI1" t="inlineStr">
+      <c r="KI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP292</t>
         </is>
       </c>
-      <c r="KJ1" t="inlineStr">
+      <c r="KJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP293</t>
         </is>
       </c>
-      <c r="KK1" t="inlineStr">
+      <c r="KK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP294</t>
         </is>
       </c>
-      <c r="KL1" t="inlineStr">
+      <c r="KL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP295</t>
         </is>
       </c>
-      <c r="KM1" t="inlineStr">
+      <c r="KM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP296</t>
         </is>
       </c>
-      <c r="KN1" t="inlineStr">
+      <c r="KN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP297</t>
         </is>
       </c>
-      <c r="KO1" t="inlineStr">
+      <c r="KO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP298</t>
         </is>
       </c>
-      <c r="KP1" t="inlineStr">
+      <c r="KP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP299</t>
         </is>
       </c>
-      <c r="KQ1" t="inlineStr">
+      <c r="KQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP300</t>
         </is>
       </c>
-      <c r="KR1" t="inlineStr">
+      <c r="KR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP301</t>
         </is>
       </c>
-      <c r="KS1" t="inlineStr">
+      <c r="KS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP302</t>
         </is>
       </c>
-      <c r="KT1" t="inlineStr">
+      <c r="KT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP303</t>
         </is>
       </c>
-      <c r="KU1" t="inlineStr">
+      <c r="KU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP304</t>
         </is>
       </c>
-      <c r="KV1" t="inlineStr">
+      <c r="KV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP305</t>
         </is>
       </c>
-      <c r="KW1" t="inlineStr">
+      <c r="KW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP306</t>
         </is>
       </c>
-      <c r="KX1" t="inlineStr">
+      <c r="KX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP307</t>
         </is>
       </c>
-      <c r="KY1" t="inlineStr">
+      <c r="KY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP308</t>
         </is>
       </c>
-      <c r="KZ1" t="inlineStr">
+      <c r="KZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP309</t>
         </is>
       </c>
-      <c r="LA1" t="inlineStr">
+      <c r="LA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP310</t>
         </is>
       </c>
-      <c r="LB1" t="inlineStr">
+      <c r="LB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP311</t>
         </is>
       </c>
-      <c r="LC1" t="inlineStr">
+      <c r="LC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP312</t>
         </is>
       </c>
-      <c r="LD1" t="inlineStr">
+      <c r="LD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP313</t>
         </is>
       </c>
-      <c r="LE1" t="inlineStr">
+      <c r="LE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP314</t>
         </is>
       </c>
-      <c r="LF1" t="inlineStr">
+      <c r="LF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP315</t>
         </is>
       </c>
-      <c r="LG1" t="inlineStr">
+      <c r="LG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP316</t>
         </is>
       </c>
-      <c r="LH1" t="inlineStr">
+      <c r="LH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP317</t>
         </is>
       </c>
-      <c r="LI1" t="inlineStr">
+      <c r="LI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP318</t>
         </is>
       </c>
-      <c r="LJ1" t="inlineStr">
+      <c r="LJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP319</t>
         </is>
       </c>
-      <c r="LK1" t="inlineStr">
+      <c r="LK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP320</t>
         </is>
       </c>
-      <c r="LL1" t="inlineStr">
+      <c r="LL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP321</t>
         </is>
       </c>
-      <c r="LM1" t="inlineStr">
+      <c r="LM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP322</t>
         </is>
       </c>
-      <c r="LN1" t="inlineStr">
+      <c r="LN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP323</t>
         </is>
       </c>
-      <c r="LO1" t="inlineStr">
+      <c r="LO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP324</t>
         </is>
       </c>
-      <c r="LP1" t="inlineStr">
+      <c r="LP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP325</t>
         </is>
       </c>
-      <c r="LQ1" t="inlineStr">
+      <c r="LQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP326</t>
         </is>
       </c>
-      <c r="LR1" t="inlineStr">
+      <c r="LR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP327</t>
         </is>
       </c>
-      <c r="LS1" t="inlineStr">
+      <c r="LS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP328</t>
         </is>
       </c>
-      <c r="LT1" t="inlineStr">
+      <c r="LT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP329</t>
         </is>
       </c>
-      <c r="LU1" t="inlineStr">
+      <c r="LU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP330</t>
         </is>
       </c>
-      <c r="LV1" t="inlineStr">
+      <c r="LV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP331</t>
         </is>
       </c>
-      <c r="LW1" t="inlineStr">
+      <c r="LW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP332</t>
         </is>
       </c>
-      <c r="LX1" t="inlineStr">
+      <c r="LX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP333</t>
         </is>
       </c>
-      <c r="LY1" t="inlineStr">
+      <c r="LY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP334</t>
         </is>
       </c>
-      <c r="LZ1" t="inlineStr">
+      <c r="LZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP335</t>
         </is>
       </c>
-      <c r="MA1" t="inlineStr">
+      <c r="MA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP336</t>
         </is>
       </c>
-      <c r="MB1" t="inlineStr">
+      <c r="MB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP337</t>
         </is>
       </c>
-      <c r="MC1" t="inlineStr">
+      <c r="MC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP338</t>
         </is>
       </c>
-      <c r="MD1" t="inlineStr">
+      <c r="MD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP339</t>
         </is>
       </c>
-      <c r="ME1" t="inlineStr">
+      <c r="ME1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP340</t>
         </is>
       </c>
-      <c r="MF1" t="inlineStr">
+      <c r="MF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP341</t>
         </is>
       </c>
-      <c r="MG1" t="inlineStr">
+      <c r="MG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP342</t>
         </is>
       </c>
-      <c r="MH1" t="inlineStr">
+      <c r="MH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP343</t>
         </is>
       </c>
-      <c r="MI1" t="inlineStr">
+      <c r="MI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP344</t>
         </is>
       </c>
-      <c r="MJ1" t="inlineStr">
+      <c r="MJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP345</t>
         </is>
       </c>
-      <c r="MK1" t="inlineStr">
+      <c r="MK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP346</t>
         </is>
       </c>
-      <c r="ML1" t="inlineStr">
+      <c r="ML1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP347</t>
         </is>
       </c>
-      <c r="MM1" t="inlineStr">
+      <c r="MM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP348</t>
         </is>
       </c>
-      <c r="MN1" t="inlineStr">
+      <c r="MN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP349</t>
         </is>
       </c>
-      <c r="MO1" t="inlineStr">
+      <c r="MO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP350</t>
         </is>
       </c>
-      <c r="MP1" t="inlineStr">
+      <c r="MP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP351</t>
         </is>
       </c>
-      <c r="MQ1" t="inlineStr">
+      <c r="MQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP352</t>
         </is>
       </c>
-      <c r="MR1" t="inlineStr">
+      <c r="MR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP353</t>
         </is>
       </c>
-      <c r="MS1" t="inlineStr">
+      <c r="MS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP354</t>
         </is>
       </c>
-      <c r="MT1" t="inlineStr">
+      <c r="MT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP355</t>
         </is>
       </c>
-      <c r="MU1" t="inlineStr">
+      <c r="MU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP356</t>
         </is>
       </c>
-      <c r="MV1" t="inlineStr">
+      <c r="MV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP357</t>
         </is>
       </c>
-      <c r="MW1" t="inlineStr">
+      <c r="MW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP358</t>
         </is>
       </c>
-      <c r="MX1" t="inlineStr">
+      <c r="MX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP359</t>
         </is>
       </c>
-      <c r="MY1" t="inlineStr">
+      <c r="MY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP360</t>
         </is>
       </c>
-      <c r="MZ1" t="inlineStr">
+      <c r="MZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP361</t>
         </is>
       </c>
-      <c r="NA1" t="inlineStr">
+      <c r="NA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP362</t>
         </is>
       </c>
-      <c r="NB1" t="inlineStr">
+      <c r="NB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP363</t>
         </is>
       </c>
-      <c r="NC1" t="inlineStr">
+      <c r="NC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP364</t>
         </is>
       </c>
-      <c r="ND1" t="inlineStr">
+      <c r="ND1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP365</t>
         </is>
       </c>
-      <c r="NE1" t="inlineStr">
+      <c r="NE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP366</t>
         </is>
       </c>
-      <c r="NF1" t="inlineStr">
+      <c r="NF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP367</t>
         </is>
       </c>
-      <c r="NG1" t="inlineStr">
+      <c r="NG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP368</t>
         </is>
       </c>
-      <c r="NH1" t="inlineStr">
+      <c r="NH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP369</t>
         </is>
       </c>
-      <c r="NI1" t="inlineStr">
+      <c r="NI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP370</t>
         </is>
       </c>
-      <c r="NJ1" t="inlineStr">
+      <c r="NJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP371</t>
         </is>
       </c>
-      <c r="NK1" t="inlineStr">
+      <c r="NK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP372</t>
         </is>
       </c>
-      <c r="NL1" t="inlineStr">
+      <c r="NL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP373</t>
         </is>
       </c>
-      <c r="NM1" t="inlineStr">
+      <c r="NM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP374</t>
         </is>
       </c>
-      <c r="NN1" t="inlineStr">
+      <c r="NN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP375</t>
         </is>
       </c>
-      <c r="NO1" t="inlineStr">
+      <c r="NO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP376</t>
         </is>
       </c>
-      <c r="NP1" t="inlineStr">
+      <c r="NP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP377</t>
         </is>
       </c>
-      <c r="NQ1" t="inlineStr">
+      <c r="NQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP378</t>
         </is>
       </c>
-      <c r="NR1" t="inlineStr">
+      <c r="NR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP379</t>
         </is>
       </c>
-      <c r="NS1" t="inlineStr">
+      <c r="NS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP380</t>
         </is>
       </c>
-      <c r="NT1" t="inlineStr">
+      <c r="NT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP381</t>
         </is>
       </c>
-      <c r="NU1" t="inlineStr">
+      <c r="NU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP382</t>
         </is>
       </c>
-      <c r="NV1" t="inlineStr">
+      <c r="NV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP383</t>
         </is>
       </c>
-      <c r="NW1" t="inlineStr">
+      <c r="NW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP384</t>
         </is>
       </c>
-      <c r="NX1" t="inlineStr">
+      <c r="NX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP385</t>
         </is>
       </c>
-      <c r="NY1" t="inlineStr">
+      <c r="NY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP386</t>
         </is>
       </c>
-      <c r="NZ1" t="inlineStr">
+      <c r="NZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP387</t>
         </is>
       </c>
-      <c r="OA1" t="inlineStr">
+      <c r="OA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP388</t>
         </is>
       </c>
-      <c r="OB1" t="inlineStr">
+      <c r="OB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP389</t>
         </is>
       </c>
-      <c r="OC1" t="inlineStr">
+      <c r="OC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP390</t>
         </is>
       </c>
-      <c r="OD1" t="inlineStr">
+      <c r="OD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP391</t>
         </is>
       </c>
-      <c r="OE1" t="inlineStr">
+      <c r="OE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP392</t>
         </is>
       </c>
-      <c r="OF1" t="inlineStr">
+      <c r="OF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP393</t>
         </is>
       </c>
-      <c r="OG1" t="inlineStr">
+      <c r="OG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP394</t>
         </is>
       </c>
-      <c r="OH1" t="inlineStr">
+      <c r="OH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP395</t>
         </is>
       </c>
-      <c r="OI1" t="inlineStr">
+      <c r="OI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP396</t>
         </is>
       </c>
-      <c r="OJ1" t="inlineStr">
+      <c r="OJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP397</t>
         </is>
       </c>
-      <c r="OK1" t="inlineStr">
+      <c r="OK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP398</t>
         </is>
       </c>
-      <c r="OL1" t="inlineStr">
+      <c r="OL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP399</t>
         </is>
       </c>
-      <c r="OM1" t="inlineStr">
+      <c r="OM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP400</t>
         </is>
       </c>
-      <c r="ON1" t="inlineStr">
+      <c r="ON1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP401</t>
         </is>
       </c>
-      <c r="OO1" t="inlineStr">
+      <c r="OO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP402</t>
         </is>
       </c>
-      <c r="OP1" t="inlineStr">
+      <c r="OP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP403</t>
         </is>
       </c>
-      <c r="OQ1" t="inlineStr">
+      <c r="OQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP404</t>
         </is>
       </c>
-      <c r="OR1" t="inlineStr">
+      <c r="OR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP405</t>
         </is>
       </c>
-      <c r="OS1" t="inlineStr">
+      <c r="OS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP406</t>
         </is>
       </c>
-      <c r="OT1" t="inlineStr">
+      <c r="OT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP407</t>
         </is>
       </c>
-      <c r="OU1" t="inlineStr">
+      <c r="OU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP408</t>
         </is>
       </c>
-      <c r="OV1" t="inlineStr">
+      <c r="OV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP409</t>
         </is>
       </c>
-      <c r="OW1" t="inlineStr">
+      <c r="OW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP410</t>
         </is>
       </c>
-      <c r="OX1" t="inlineStr">
+      <c r="OX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP411</t>
         </is>
       </c>
-      <c r="OY1" t="inlineStr">
+      <c r="OY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP412</t>
         </is>
       </c>
-      <c r="OZ1" t="inlineStr">
+      <c r="OZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP413</t>
         </is>
       </c>
-      <c r="PA1" t="inlineStr">
+      <c r="PA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP414</t>
         </is>
       </c>
-      <c r="PB1" t="inlineStr">
+      <c r="PB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP415</t>
         </is>
       </c>
-      <c r="PC1" t="inlineStr">
+      <c r="PC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP416</t>
         </is>
       </c>
-      <c r="PD1" t="inlineStr">
+      <c r="PD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP417</t>
         </is>
       </c>
-      <c r="PE1" t="inlineStr">
+      <c r="PE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP418</t>
         </is>
       </c>
-      <c r="PF1" t="inlineStr">
+      <c r="PF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP419</t>
         </is>
       </c>
-      <c r="PG1" t="inlineStr">
+      <c r="PG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP420</t>
         </is>
       </c>
-      <c r="PH1" t="inlineStr">
+      <c r="PH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP421</t>
         </is>
       </c>
-      <c r="PI1" t="inlineStr">
+      <c r="PI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP422</t>
         </is>
       </c>
-      <c r="PJ1" t="inlineStr">
+      <c r="PJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP423</t>
         </is>
       </c>
-      <c r="PK1" t="inlineStr">
+      <c r="PK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP424</t>
         </is>
       </c>
-      <c r="PL1" t="inlineStr">
+      <c r="PL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP425</t>
         </is>
       </c>
-      <c r="PM1" t="inlineStr">
+      <c r="PM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP426</t>
         </is>
       </c>
-      <c r="PN1" t="inlineStr">
+      <c r="PN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP427</t>
         </is>
       </c>
-      <c r="PO1" t="inlineStr">
+      <c r="PO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP428</t>
         </is>
       </c>
-      <c r="PP1" t="inlineStr">
+      <c r="PP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP429</t>
         </is>
       </c>
-      <c r="PQ1" t="inlineStr">
+      <c r="PQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP430</t>
         </is>
       </c>
-      <c r="PR1" t="inlineStr">
+      <c r="PR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP431</t>
         </is>
       </c>
-      <c r="PS1" t="inlineStr">
+      <c r="PS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP432</t>
         </is>
       </c>
-      <c r="PT1" t="inlineStr">
+      <c r="PT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP433</t>
         </is>
       </c>
-      <c r="PU1" t="inlineStr">
+      <c r="PU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP434</t>
         </is>
       </c>
-      <c r="PV1" t="inlineStr">
+      <c r="PV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP435</t>
         </is>
       </c>
-      <c r="PW1" t="inlineStr">
+      <c r="PW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP436</t>
         </is>
       </c>
-      <c r="PX1" t="inlineStr">
+      <c r="PX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP437</t>
         </is>
       </c>
-      <c r="PY1" t="inlineStr">
+      <c r="PY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP438</t>
         </is>
       </c>
-      <c r="PZ1" t="inlineStr">
+      <c r="PZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP439</t>
         </is>
       </c>
-      <c r="QA1" t="inlineStr">
+      <c r="QA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP440</t>
         </is>
       </c>
-      <c r="QB1" t="inlineStr">
+      <c r="QB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP441</t>
         </is>
       </c>
-      <c r="QC1" t="inlineStr">
+      <c r="QC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP442</t>
         </is>
       </c>
-      <c r="QD1" t="inlineStr">
+      <c r="QD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP443</t>
         </is>
       </c>
-      <c r="QE1" t="inlineStr">
+      <c r="QE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP444</t>
         </is>
       </c>
-      <c r="QF1" t="inlineStr">
+      <c r="QF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP445</t>
         </is>
       </c>
-      <c r="QG1" t="inlineStr">
+      <c r="QG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP446</t>
         </is>
       </c>
-      <c r="QH1" t="inlineStr">
+      <c r="QH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP447</t>
         </is>
       </c>
-      <c r="QI1" t="inlineStr">
+      <c r="QI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP448</t>
         </is>
       </c>
-      <c r="QJ1" t="inlineStr">
+      <c r="QJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP449</t>
         </is>
       </c>
-      <c r="QK1" t="inlineStr">
+      <c r="QK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP450</t>
         </is>
       </c>
-      <c r="QL1" t="inlineStr">
+      <c r="QL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP451</t>
         </is>
       </c>
-      <c r="QM1" t="inlineStr">
+      <c r="QM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP452</t>
         </is>
       </c>
-      <c r="QN1" t="inlineStr">
+      <c r="QN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP453</t>
         </is>
       </c>
-      <c r="QO1" t="inlineStr">
+      <c r="QO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP454</t>
         </is>
       </c>
-      <c r="QP1" t="inlineStr">
+      <c r="QP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP455</t>
         </is>
       </c>
-      <c r="QQ1" t="inlineStr">
+      <c r="QQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP456</t>
         </is>
       </c>
-      <c r="QR1" t="inlineStr">
+      <c r="QR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP457</t>
         </is>
       </c>
-      <c r="QS1" t="inlineStr">
+      <c r="QS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP458</t>
         </is>
       </c>
-      <c r="QT1" t="inlineStr">
+      <c r="QT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP459</t>
         </is>
       </c>
-      <c r="QU1" t="inlineStr">
+      <c r="QU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP460</t>
         </is>
       </c>
-      <c r="QV1" t="inlineStr">
+      <c r="QV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP461</t>
         </is>
       </c>
-      <c r="QW1" t="inlineStr">
+      <c r="QW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP462</t>
         </is>
       </c>
-      <c r="QX1" t="inlineStr">
+      <c r="QX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP463</t>
         </is>
       </c>
-      <c r="QY1" t="inlineStr">
+      <c r="QY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP464</t>
         </is>
       </c>
-      <c r="QZ1" t="inlineStr">
+      <c r="QZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP465</t>
         </is>
       </c>
-      <c r="RA1" t="inlineStr">
+      <c r="RA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP466</t>
         </is>
       </c>
-      <c r="RB1" t="inlineStr">
+      <c r="RB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP467</t>
         </is>
       </c>
-      <c r="RC1" t="inlineStr">
+      <c r="RC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP468</t>
         </is>
       </c>
-      <c r="RD1" t="inlineStr">
+      <c r="RD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP469</t>
         </is>
       </c>
-      <c r="RE1" t="inlineStr">
+      <c r="RE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP470</t>
         </is>
       </c>
-      <c r="RF1" t="inlineStr">
+      <c r="RF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP471</t>
         </is>
       </c>
-      <c r="RG1" t="inlineStr">
+      <c r="RG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP472</t>
         </is>
       </c>
-      <c r="RH1" t="inlineStr">
+      <c r="RH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP473</t>
         </is>
       </c>
-      <c r="RI1" t="inlineStr">
+      <c r="RI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP474</t>
         </is>
       </c>
-      <c r="RJ1" t="inlineStr">
+      <c r="RJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP475</t>
         </is>
       </c>
-      <c r="RK1" t="inlineStr">
+      <c r="RK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP476</t>
         </is>
       </c>
-      <c r="RL1" t="inlineStr">
+      <c r="RL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP477</t>
         </is>
       </c>
-      <c r="RM1" t="inlineStr">
+      <c r="RM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP478</t>
         </is>
       </c>
-      <c r="RN1" t="inlineStr">
+      <c r="RN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP479</t>
         </is>
       </c>
-      <c r="RO1" t="inlineStr">
+      <c r="RO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP480</t>
         </is>
       </c>
-      <c r="RP1" t="inlineStr">
+      <c r="RP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP481</t>
         </is>
       </c>
-      <c r="RQ1" t="inlineStr">
+      <c r="RQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP482</t>
         </is>
       </c>
-      <c r="RR1" t="inlineStr">
+      <c r="RR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP483</t>
         </is>
       </c>
-      <c r="RS1" t="inlineStr">
+      <c r="RS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP484</t>
         </is>
       </c>
-      <c r="RT1" t="inlineStr">
+      <c r="RT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP485</t>
         </is>
       </c>
-      <c r="RU1" t="inlineStr">
+      <c r="RU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP486</t>
         </is>
       </c>
-      <c r="RV1" t="inlineStr">
+      <c r="RV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP487</t>
         </is>
       </c>
-      <c r="RW1" t="inlineStr">
+      <c r="RW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP488</t>
         </is>
       </c>
-      <c r="RX1" t="inlineStr">
+      <c r="RX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP489</t>
         </is>
       </c>
-      <c r="RY1" t="inlineStr">
+      <c r="RY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP490</t>
         </is>
       </c>
-      <c r="RZ1" t="inlineStr">
+      <c r="RZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP491</t>
         </is>
       </c>
-      <c r="SA1" t="inlineStr">
+      <c r="SA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP492</t>
         </is>
       </c>
-      <c r="SB1" t="inlineStr">
+      <c r="SB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP493</t>
         </is>
       </c>
-      <c r="SC1" t="inlineStr">
+      <c r="SC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP494</t>
         </is>
       </c>
-      <c r="SD1" t="inlineStr">
+      <c r="SD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP495</t>
         </is>
       </c>
-      <c r="SE1" t="inlineStr">
+      <c r="SE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP496</t>
         </is>
       </c>
-      <c r="SF1" t="inlineStr">
+      <c r="SF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP497</t>
         </is>
       </c>
-      <c r="SG1" t="inlineStr">
+      <c r="SG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP498</t>
         </is>
       </c>
-      <c r="SH1" t="inlineStr">
+      <c r="SH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP499</t>
         </is>
       </c>
-      <c r="SI1" t="inlineStr">
+      <c r="SI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP500</t>
         </is>
       </c>
-      <c r="SJ1" t="inlineStr">
+      <c r="SJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP501</t>
         </is>
       </c>
-      <c r="SK1" t="inlineStr">
+      <c r="SK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP502</t>
         </is>
       </c>
-      <c r="SL1" t="inlineStr">
+      <c r="SL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP503</t>
         </is>
       </c>
-      <c r="SM1" t="inlineStr">
+      <c r="SM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP504</t>
         </is>
       </c>
-      <c r="SN1" t="inlineStr">
+      <c r="SN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP505</t>
         </is>
       </c>
-      <c r="SO1" t="inlineStr">
+      <c r="SO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP506</t>
         </is>
       </c>
-      <c r="SP1" t="inlineStr">
+      <c r="SP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP507</t>
         </is>
       </c>
-      <c r="SQ1" t="inlineStr">
+      <c r="SQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP508</t>
         </is>
       </c>
-      <c r="SR1" t="inlineStr">
+      <c r="SR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP509</t>
         </is>
       </c>
-      <c r="SS1" t="inlineStr">
+      <c r="SS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP510</t>
         </is>
       </c>
-      <c r="ST1" t="inlineStr">
+      <c r="ST1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP511</t>
         </is>
       </c>
-      <c r="SU1" t="inlineStr">
+      <c r="SU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP512</t>
         </is>
       </c>
-      <c r="SV1" t="inlineStr">
+      <c r="SV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP513</t>
         </is>
       </c>
-      <c r="SW1" t="inlineStr">
+      <c r="SW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP514</t>
         </is>
       </c>
-      <c r="SX1" t="inlineStr">
+      <c r="SX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP515</t>
         </is>
       </c>
-      <c r="SY1" t="inlineStr">
+      <c r="SY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP516</t>
         </is>
       </c>
-      <c r="SZ1" t="inlineStr">
+      <c r="SZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP517</t>
         </is>
       </c>
-      <c r="TA1" t="inlineStr">
+      <c r="TA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP518</t>
         </is>
       </c>
-      <c r="TB1" t="inlineStr">
+      <c r="TB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP519</t>
         </is>
       </c>
-      <c r="TC1" t="inlineStr">
+      <c r="TC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP520</t>
         </is>
       </c>
-      <c r="TD1" t="inlineStr">
+      <c r="TD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP521</t>
         </is>
       </c>
-      <c r="TE1" t="inlineStr">
+      <c r="TE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP522</t>
         </is>
       </c>
-      <c r="TF1" t="inlineStr">
+      <c r="TF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP523</t>
         </is>
       </c>
-      <c r="TG1" t="inlineStr">
+      <c r="TG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP524</t>
         </is>
       </c>
-      <c r="TH1" t="inlineStr">
+      <c r="TH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP525</t>
         </is>
       </c>
-      <c r="TI1" t="inlineStr">
+      <c r="TI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP526</t>
         </is>
       </c>
-      <c r="TJ1" t="inlineStr">
+      <c r="TJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP527</t>
         </is>
       </c>
-      <c r="TK1" t="inlineStr">
+      <c r="TK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP528</t>
         </is>
       </c>
-      <c r="TL1" t="inlineStr">
+      <c r="TL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP529</t>
         </is>
       </c>
-      <c r="TM1" t="inlineStr">
+      <c r="TM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP530</t>
         </is>
       </c>
-      <c r="TN1" t="inlineStr">
+      <c r="TN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP531</t>
         </is>
       </c>
-      <c r="TO1" t="inlineStr">
+      <c r="TO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP532</t>
         </is>
       </c>
-      <c r="TP1" t="inlineStr">
+      <c r="TP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP533</t>
         </is>
       </c>
-      <c r="TQ1" t="inlineStr">
+      <c r="TQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP534</t>
         </is>
       </c>
-      <c r="TR1" t="inlineStr">
+      <c r="TR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP535</t>
         </is>
       </c>
-      <c r="TS1" t="inlineStr">
+      <c r="TS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP536</t>
         </is>
       </c>
-      <c r="TT1" t="inlineStr">
+      <c r="TT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP537</t>
         </is>
       </c>
-      <c r="TU1" t="inlineStr">
+      <c r="TU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP538</t>
         </is>
       </c>
-      <c r="TV1" t="inlineStr">
+      <c r="TV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP539</t>
         </is>
       </c>
-      <c r="TW1" t="inlineStr">
+      <c r="TW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP540</t>
         </is>
       </c>
-      <c r="TX1" t="inlineStr">
+      <c r="TX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP541</t>
         </is>
       </c>
-      <c r="TY1" t="inlineStr">
+      <c r="TY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP542</t>
         </is>
       </c>
-      <c r="TZ1" t="inlineStr">
+      <c r="TZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP543</t>
         </is>
       </c>
-      <c r="UA1" t="inlineStr">
+      <c r="UA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP544</t>
         </is>
       </c>
-      <c r="UB1" t="inlineStr">
+      <c r="UB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP545</t>
         </is>
       </c>
-      <c r="UC1" t="inlineStr">
+      <c r="UC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP546</t>
         </is>
       </c>
-      <c r="UD1" t="inlineStr">
+      <c r="UD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP547</t>
         </is>
       </c>
-      <c r="UE1" t="inlineStr">
+      <c r="UE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP548</t>
         </is>
       </c>
-      <c r="UF1" t="inlineStr">
+      <c r="UF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP549</t>
         </is>
       </c>
-      <c r="UG1" t="inlineStr">
+      <c r="UG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP550</t>
         </is>
       </c>
-      <c r="UH1" t="inlineStr">
+      <c r="UH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP551</t>
         </is>
       </c>
-      <c r="UI1" t="inlineStr">
+      <c r="UI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP552</t>
         </is>
       </c>
-      <c r="UJ1" t="inlineStr">
+      <c r="UJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP553</t>
         </is>
       </c>
-      <c r="UK1" t="inlineStr">
+      <c r="UK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP554</t>
         </is>
       </c>
-      <c r="UL1" t="inlineStr">
+      <c r="UL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP555</t>
         </is>
       </c>
-      <c r="UM1" t="inlineStr">
+      <c r="UM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP556</t>
         </is>
       </c>
-      <c r="UN1" t="inlineStr">
+      <c r="UN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP557</t>
         </is>
       </c>
-      <c r="UO1" t="inlineStr">
+      <c r="UO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP558</t>
         </is>
       </c>
-      <c r="UP1" t="inlineStr">
+      <c r="UP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP559</t>
         </is>
       </c>
-      <c r="UQ1" t="inlineStr">
+      <c r="UQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP560</t>
         </is>
       </c>
-      <c r="UR1" t="inlineStr">
+      <c r="UR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP561</t>
         </is>
       </c>
-      <c r="US1" t="inlineStr">
+      <c r="US1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP562</t>
         </is>
       </c>
-      <c r="UT1" t="inlineStr">
+      <c r="UT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP563</t>
         </is>
       </c>
-      <c r="UU1" t="inlineStr">
+      <c r="UU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP564</t>
         </is>
       </c>
-      <c r="UV1" t="inlineStr">
+      <c r="UV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP565</t>
         </is>
       </c>
-      <c r="UW1" t="inlineStr">
+      <c r="UW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP566</t>
         </is>
       </c>
-      <c r="UX1" t="inlineStr">
+      <c r="UX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP567</t>
         </is>
       </c>
-      <c r="UY1" t="inlineStr">
+      <c r="UY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP568</t>
         </is>
       </c>
-      <c r="UZ1" t="inlineStr">
+      <c r="UZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP569</t>
         </is>
       </c>
-      <c r="VA1" t="inlineStr">
+      <c r="VA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP570</t>
         </is>
       </c>
-      <c r="VB1" t="inlineStr">
+      <c r="VB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP571</t>
         </is>
       </c>
-      <c r="VC1" t="inlineStr">
+      <c r="VC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP572</t>
         </is>
       </c>
-      <c r="VD1" t="inlineStr">
+      <c r="VD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP573</t>
         </is>
       </c>
-      <c r="VE1" t="inlineStr">
+      <c r="VE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP574</t>
         </is>
       </c>
-      <c r="VF1" t="inlineStr">
+      <c r="VF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP575</t>
         </is>
       </c>
-      <c r="VG1" t="inlineStr">
+      <c r="VG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP576</t>
         </is>
       </c>
-      <c r="VH1" t="inlineStr">
+      <c r="VH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP577</t>
         </is>
       </c>
-      <c r="VI1" t="inlineStr">
+      <c r="VI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP578</t>
         </is>
       </c>
-      <c r="VJ1" t="inlineStr">
+      <c r="VJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP579</t>
         </is>
       </c>
-      <c r="VK1" t="inlineStr">
+      <c r="VK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP580</t>
         </is>
       </c>
-      <c r="VL1" t="inlineStr">
+      <c r="VL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP581</t>
         </is>
       </c>
-      <c r="VM1" t="inlineStr">
+      <c r="VM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP582</t>
         </is>
       </c>
-      <c r="VN1" t="inlineStr">
+      <c r="VN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP583</t>
         </is>
       </c>
-      <c r="VO1" t="inlineStr">
+      <c r="VO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP584</t>
         </is>
       </c>
-      <c r="VP1" t="inlineStr">
+      <c r="VP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP585</t>
         </is>
       </c>
-      <c r="VQ1" t="inlineStr">
+      <c r="VQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP586</t>
         </is>
       </c>
-      <c r="VR1" t="inlineStr">
+      <c r="VR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP587</t>
         </is>
       </c>
-      <c r="VS1" t="inlineStr">
+      <c r="VS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP588</t>
         </is>
       </c>
-      <c r="VT1" t="inlineStr">
+      <c r="VT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP589</t>
         </is>
       </c>
-      <c r="VU1" t="inlineStr">
+      <c r="VU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP590</t>
         </is>
       </c>
-      <c r="VV1" t="inlineStr">
+      <c r="VV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP591</t>
         </is>
       </c>
-      <c r="VW1" t="inlineStr">
+      <c r="VW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP592</t>
         </is>
       </c>
-      <c r="VX1" t="inlineStr">
+      <c r="VX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP593</t>
         </is>
       </c>
-      <c r="VY1" t="inlineStr">
+      <c r="VY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP594</t>
         </is>
       </c>
-      <c r="VZ1" t="inlineStr">
+      <c r="VZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP595</t>
         </is>
       </c>
-      <c r="WA1" t="inlineStr">
+      <c r="WA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP596</t>
         </is>
       </c>
-      <c r="WB1" t="inlineStr">
+      <c r="WB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP597</t>
         </is>
       </c>
-      <c r="WC1" t="inlineStr">
+      <c r="WC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP598</t>
         </is>
       </c>
-      <c r="WD1" t="inlineStr">
+      <c r="WD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP599</t>
         </is>
       </c>
-      <c r="WE1" t="inlineStr">
+      <c r="WE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP600</t>
         </is>
       </c>
-      <c r="WF1" t="inlineStr">
+      <c r="WF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP601</t>
         </is>
       </c>
-      <c r="WG1" t="inlineStr">
+      <c r="WG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP602</t>
         </is>
       </c>
-      <c r="WH1" t="inlineStr">
+      <c r="WH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP603</t>
         </is>
       </c>
-      <c r="WI1" t="inlineStr">
+      <c r="WI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP604</t>
         </is>
       </c>
-      <c r="WJ1" t="inlineStr">
+      <c r="WJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP605</t>
         </is>
       </c>
-      <c r="WK1" t="inlineStr">
+      <c r="WK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP606</t>
         </is>
       </c>
-      <c r="WL1" t="inlineStr">
+      <c r="WL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP607</t>
         </is>
       </c>
-      <c r="WM1" t="inlineStr">
+      <c r="WM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP608</t>
         </is>
       </c>
-      <c r="WN1" t="inlineStr">
+      <c r="WN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP609</t>
         </is>
       </c>
-      <c r="WO1" t="inlineStr">
+      <c r="WO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP610</t>
         </is>
       </c>
-      <c r="WP1" t="inlineStr">
+      <c r="WP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP611</t>
         </is>
       </c>
-      <c r="WQ1" t="inlineStr">
+      <c r="WQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP612</t>
         </is>
       </c>
-      <c r="WR1" t="inlineStr">
+      <c r="WR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP613</t>
         </is>
       </c>
-      <c r="WS1" t="inlineStr">
+      <c r="WS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP614</t>
         </is>
       </c>
-      <c r="WT1" t="inlineStr">
+      <c r="WT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP615</t>
         </is>
       </c>
-      <c r="WU1" t="inlineStr">
+      <c r="WU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP616</t>
         </is>
       </c>
-      <c r="WV1" t="inlineStr">
+      <c r="WV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP617</t>
         </is>
       </c>
-      <c r="WW1" t="inlineStr">
+      <c r="WW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP618</t>
         </is>
       </c>
-      <c r="WX1" t="inlineStr">
+      <c r="WX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP619</t>
         </is>
       </c>
-      <c r="WY1" t="inlineStr">
+      <c r="WY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP620</t>
         </is>
       </c>
-      <c r="WZ1" t="inlineStr">
+      <c r="WZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP621</t>
         </is>
       </c>
-      <c r="XA1" t="inlineStr">
+      <c r="XA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP622</t>
         </is>
       </c>
-      <c r="XB1" t="inlineStr">
+      <c r="XB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP623</t>
         </is>
       </c>
-      <c r="XC1" t="inlineStr">
+      <c r="XC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP624</t>
         </is>
       </c>
-      <c r="XD1" t="inlineStr">
+      <c r="XD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP625</t>
         </is>
       </c>
-      <c r="XE1" t="inlineStr">
+      <c r="XE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP626</t>
         </is>
       </c>
-      <c r="XF1" t="inlineStr">
+      <c r="XF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP627</t>
         </is>
       </c>
-      <c r="XG1" t="inlineStr">
+      <c r="XG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP628</t>
         </is>
       </c>
-      <c r="XH1" t="inlineStr">
+      <c r="XH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP629</t>
         </is>
       </c>
-      <c r="XI1" t="inlineStr">
+      <c r="XI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP630</t>
         </is>
       </c>
-      <c r="XJ1" t="inlineStr">
+      <c r="XJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP631</t>
         </is>
       </c>
-      <c r="XK1" t="inlineStr">
+      <c r="XK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP632</t>
         </is>
       </c>
-      <c r="XL1" t="inlineStr">
+      <c r="XL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP633</t>
         </is>
       </c>
-      <c r="XM1" t="inlineStr">
+      <c r="XM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP634</t>
         </is>
       </c>
-      <c r="XN1" t="inlineStr">
+      <c r="XN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP635</t>
         </is>
       </c>
-      <c r="XO1" t="inlineStr">
+      <c r="XO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP636</t>
         </is>
       </c>
-      <c r="XP1" t="inlineStr">
+      <c r="XP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP637</t>
         </is>
       </c>
-      <c r="XQ1" t="inlineStr">
+      <c r="XQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP638</t>
         </is>
       </c>
-      <c r="XR1" t="inlineStr">
+      <c r="XR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP639</t>
         </is>
       </c>
-      <c r="XS1" t="inlineStr">
+      <c r="XS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP640</t>
         </is>
       </c>
-      <c r="XT1" t="inlineStr">
+      <c r="XT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP641</t>
         </is>
       </c>
-      <c r="XU1" t="inlineStr">
+      <c r="XU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP642</t>
         </is>
       </c>
-      <c r="XV1" t="inlineStr">
+      <c r="XV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP643</t>
         </is>
       </c>
-      <c r="XW1" t="inlineStr">
+      <c r="XW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP644</t>
         </is>
       </c>
-      <c r="XX1" t="inlineStr">
+      <c r="XX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP645</t>
         </is>
       </c>
-      <c r="XY1" t="inlineStr">
+      <c r="XY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP646</t>
         </is>
       </c>
-      <c r="XZ1" t="inlineStr">
+      <c r="XZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP647</t>
         </is>
       </c>
-      <c r="YA1" t="inlineStr">
+      <c r="YA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP648</t>
         </is>
       </c>
-      <c r="YB1" t="inlineStr">
+      <c r="YB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP649</t>
         </is>
       </c>
-      <c r="YC1" t="inlineStr">
+      <c r="YC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP650</t>
         </is>
       </c>
-      <c r="YD1" t="inlineStr">
+      <c r="YD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP651</t>
         </is>
       </c>
-      <c r="YE1" t="inlineStr">
+      <c r="YE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP652</t>
         </is>
       </c>
-      <c r="YF1" t="inlineStr">
+      <c r="YF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP653</t>
         </is>
       </c>
-      <c r="YG1" t="inlineStr">
+      <c r="YG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP654</t>
         </is>
       </c>
-      <c r="YH1" t="inlineStr">
+      <c r="YH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP655</t>
         </is>
       </c>
-      <c r="YI1" t="inlineStr">
+      <c r="YI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP656</t>
         </is>
       </c>
-      <c r="YJ1" t="inlineStr">
+      <c r="YJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP657</t>
         </is>
       </c>
-      <c r="YK1" t="inlineStr">
+      <c r="YK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP658</t>
         </is>
       </c>
-      <c r="YL1" t="inlineStr">
+      <c r="YL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP659</t>
         </is>
       </c>
-      <c r="YM1" t="inlineStr">
+      <c r="YM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP660</t>
         </is>
       </c>
-      <c r="YN1" t="inlineStr">
+      <c r="YN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP661</t>
         </is>
       </c>
-      <c r="YO1" t="inlineStr">
+      <c r="YO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP662</t>
         </is>
       </c>
-      <c r="YP1" t="inlineStr">
+      <c r="YP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP663</t>
         </is>
       </c>
-      <c r="YQ1" t="inlineStr">
+      <c r="YQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP664</t>
         </is>
       </c>
-      <c r="YR1" t="inlineStr">
+      <c r="YR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP665</t>
         </is>
       </c>
-      <c r="YS1" t="inlineStr">
+      <c r="YS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP666</t>
         </is>
       </c>
-      <c r="YT1" t="inlineStr">
+      <c r="YT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP667</t>
         </is>
       </c>
-      <c r="YU1" t="inlineStr">
+      <c r="YU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP668</t>
         </is>
       </c>
-      <c r="YV1" t="inlineStr">
+      <c r="YV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP669</t>
         </is>
       </c>
-      <c r="YW1" t="inlineStr">
+      <c r="YW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP670</t>
         </is>
       </c>
-      <c r="YX1" t="inlineStr">
+      <c r="YX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP671</t>
         </is>
       </c>
-      <c r="YY1" t="inlineStr">
+      <c r="YY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP672</t>
         </is>
       </c>
-      <c r="YZ1" t="inlineStr">
+      <c r="YZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP673</t>
         </is>
       </c>
-      <c r="ZA1" t="inlineStr">
+      <c r="ZA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP674</t>
         </is>
       </c>
-      <c r="ZB1" t="inlineStr">
+      <c r="ZB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP675</t>
         </is>
       </c>
-      <c r="ZC1" t="inlineStr">
+      <c r="ZC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP676</t>
         </is>
       </c>
-      <c r="ZD1" t="inlineStr">
+      <c r="ZD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP677</t>
         </is>
       </c>
-      <c r="ZE1" t="inlineStr">
+      <c r="ZE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP678</t>
         </is>
       </c>
-      <c r="ZF1" t="inlineStr">
+      <c r="ZF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP679</t>
         </is>
       </c>
-      <c r="ZG1" t="inlineStr">
+      <c r="ZG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP680</t>
         </is>
       </c>
-      <c r="ZH1" t="inlineStr">
+      <c r="ZH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP681</t>
         </is>
       </c>
-      <c r="ZI1" t="inlineStr">
+      <c r="ZI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP682</t>
         </is>
       </c>
-      <c r="ZJ1" t="inlineStr">
+      <c r="ZJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP683</t>
         </is>
       </c>
-      <c r="ZK1" t="inlineStr">
+      <c r="ZK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP684</t>
         </is>
       </c>
-      <c r="ZL1" t="inlineStr">
+      <c r="ZL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP685</t>
         </is>
       </c>
-      <c r="ZM1" t="inlineStr">
+      <c r="ZM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP686</t>
         </is>
       </c>
-      <c r="ZN1" t="inlineStr">
+      <c r="ZN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP687</t>
         </is>
       </c>
-      <c r="ZO1" t="inlineStr">
+      <c r="ZO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP688</t>
         </is>
       </c>
-      <c r="ZP1" t="inlineStr">
+      <c r="ZP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP689</t>
         </is>
       </c>
-      <c r="ZQ1" t="inlineStr">
+      <c r="ZQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP690</t>
         </is>
       </c>
-      <c r="ZR1" t="inlineStr">
+      <c r="ZR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP691</t>
         </is>
       </c>
-      <c r="ZS1" t="inlineStr">
+      <c r="ZS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP692</t>
         </is>
       </c>
-      <c r="ZT1" t="inlineStr">
+      <c r="ZT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP693</t>
         </is>
       </c>
-      <c r="ZU1" t="inlineStr">
+      <c r="ZU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP694</t>
         </is>
       </c>
-      <c r="ZV1" t="inlineStr">
+      <c r="ZV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP695</t>
         </is>
       </c>
-      <c r="ZW1" t="inlineStr">
+      <c r="ZW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP696</t>
         </is>
       </c>
-      <c r="ZX1" t="inlineStr">
+      <c r="ZX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP697</t>
         </is>
       </c>
-      <c r="ZY1" t="inlineStr">
+      <c r="ZY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP698</t>
         </is>
       </c>
-      <c r="ZZ1" t="inlineStr">
+      <c r="ZZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP699</t>
         </is>
       </c>
-      <c r="AAA1" t="inlineStr">
+      <c r="AAA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP700</t>
         </is>
       </c>
-      <c r="AAB1" t="inlineStr">
+      <c r="AAB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP701</t>
         </is>
       </c>
-      <c r="AAC1" t="inlineStr">
+      <c r="AAC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP702</t>
         </is>
       </c>
-      <c r="AAD1" t="inlineStr">
+      <c r="AAD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP703</t>
         </is>
       </c>
-      <c r="AAE1" t="inlineStr">
+      <c r="AAE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP704</t>
         </is>
       </c>
-      <c r="AAF1" t="inlineStr">
+      <c r="AAF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP705</t>
         </is>
       </c>
-      <c r="AAG1" t="inlineStr">
+      <c r="AAG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP706</t>
         </is>
       </c>
-      <c r="AAH1" t="inlineStr">
+      <c r="AAH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP707</t>
         </is>
       </c>
-      <c r="AAI1" t="inlineStr">
+      <c r="AAI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP708</t>
         </is>
       </c>
-      <c r="AAJ1" t="inlineStr">
+      <c r="AAJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP709</t>
         </is>
       </c>
-      <c r="AAK1" t="inlineStr">
+      <c r="AAK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP710</t>
         </is>
       </c>
-      <c r="AAL1" t="inlineStr">
+      <c r="AAL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP711</t>
         </is>
       </c>
-      <c r="AAM1" t="inlineStr">
+      <c r="AAM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP712</t>
         </is>
       </c>
-      <c r="AAN1" t="inlineStr">
+      <c r="AAN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP713</t>
         </is>
       </c>
-      <c r="AAO1" t="inlineStr">
+      <c r="AAO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP714</t>
         </is>
       </c>
-      <c r="AAP1" t="inlineStr">
+      <c r="AAP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP715</t>
         </is>
       </c>
-      <c r="AAQ1" t="inlineStr">
+      <c r="AAQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP716</t>
         </is>
       </c>
-      <c r="AAR1" t="inlineStr">
+      <c r="AAR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP717</t>
         </is>
       </c>
-      <c r="AAS1" t="inlineStr">
+      <c r="AAS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP718</t>
         </is>
       </c>
-      <c r="AAT1" t="inlineStr">
+      <c r="AAT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP719</t>
         </is>
       </c>
-      <c r="AAU1" t="inlineStr">
+      <c r="AAU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP720</t>
         </is>
       </c>
-      <c r="AAV1" t="inlineStr">
+      <c r="AAV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP721</t>
         </is>
       </c>
-      <c r="AAW1" t="inlineStr">
+      <c r="AAW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP722</t>
         </is>
       </c>
-      <c r="AAX1" t="inlineStr">
+      <c r="AAX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP723</t>
         </is>
       </c>
-      <c r="AAY1" t="inlineStr">
+      <c r="AAY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP724</t>
         </is>
       </c>
-      <c r="AAZ1" t="inlineStr">
+      <c r="AAZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP725</t>
         </is>
       </c>
-      <c r="ABA1" t="inlineStr">
+      <c r="ABA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP726</t>
         </is>
       </c>
-      <c r="ABB1" t="inlineStr">
+      <c r="ABB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP727</t>
         </is>
       </c>
-      <c r="ABC1" t="inlineStr">
+      <c r="ABC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP728</t>
         </is>
       </c>
-      <c r="ABD1" t="inlineStr">
+      <c r="ABD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP729</t>
         </is>
       </c>
-      <c r="ABE1" t="inlineStr">
+      <c r="ABE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP730</t>
         </is>
       </c>
-      <c r="ABF1" t="inlineStr">
+      <c r="ABF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP731</t>
         </is>
       </c>
-      <c r="ABG1" t="inlineStr">
+      <c r="ABG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP732</t>
         </is>
       </c>
-      <c r="ABH1" t="inlineStr">
+      <c r="ABH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP733</t>
         </is>
       </c>
-      <c r="ABI1" t="inlineStr">
+      <c r="ABI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP734</t>
         </is>
       </c>
-      <c r="ABJ1" t="inlineStr">
+      <c r="ABJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP735</t>
         </is>
       </c>
-      <c r="ABK1" t="inlineStr">
+      <c r="ABK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP736</t>
         </is>
       </c>
-      <c r="ABL1" t="inlineStr">
+      <c r="ABL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP737</t>
         </is>
       </c>
-      <c r="ABM1" t="inlineStr">
+      <c r="ABM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP738</t>
         </is>
       </c>
-      <c r="ABN1" t="inlineStr">
+      <c r="ABN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP739</t>
         </is>
       </c>
-      <c r="ABO1" t="inlineStr">
+      <c r="ABO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP740</t>
         </is>
       </c>
-      <c r="ABP1" t="inlineStr">
+      <c r="ABP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP741</t>
         </is>
       </c>
-      <c r="ABQ1" t="inlineStr">
+      <c r="ABQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP742</t>
         </is>
       </c>
-      <c r="ABR1" t="inlineStr">
+      <c r="ABR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP743</t>
         </is>
       </c>
-      <c r="ABS1" t="inlineStr">
+      <c r="ABS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP744</t>
         </is>
       </c>
-      <c r="ABT1" t="inlineStr">
+      <c r="ABT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP745</t>
         </is>
       </c>
-      <c r="ABU1" t="inlineStr">
+      <c r="ABU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP746</t>
         </is>
       </c>
-      <c r="ABV1" t="inlineStr">
+      <c r="ABV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP747</t>
         </is>
       </c>
-      <c r="ABW1" t="inlineStr">
+      <c r="ABW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP748</t>
         </is>
       </c>
-      <c r="ABX1" t="inlineStr">
+      <c r="ABX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP749</t>
         </is>
       </c>
-      <c r="ABY1" t="inlineStr">
+      <c r="ABY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP750</t>
         </is>
       </c>
-      <c r="ABZ1" t="inlineStr">
+      <c r="ABZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP751</t>
         </is>
       </c>
-      <c r="ACA1" t="inlineStr">
+      <c r="ACA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP752</t>
         </is>
       </c>
-      <c r="ACB1" t="inlineStr">
+      <c r="ACB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP753</t>
         </is>
       </c>
-      <c r="ACC1" t="inlineStr">
+      <c r="ACC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP754</t>
         </is>
       </c>
-      <c r="ACD1" t="inlineStr">
+      <c r="ACD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP755</t>
         </is>
       </c>
-      <c r="ACE1" t="inlineStr">
+      <c r="ACE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP756</t>
         </is>
       </c>
-      <c r="ACF1" t="inlineStr">
+      <c r="ACF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP757</t>
         </is>
       </c>
-      <c r="ACG1" t="inlineStr">
+      <c r="ACG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP758</t>
         </is>
       </c>
-      <c r="ACH1" t="inlineStr">
+      <c r="ACH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP759</t>
         </is>
       </c>
-      <c r="ACI1" t="inlineStr">
+      <c r="ACI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP760</t>
         </is>
       </c>
-      <c r="ACJ1" t="inlineStr">
+      <c r="ACJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP761</t>
         </is>
       </c>
-      <c r="ACK1" t="inlineStr">
+      <c r="ACK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP762</t>
         </is>
       </c>
-      <c r="ACL1" t="inlineStr">
+      <c r="ACL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP763</t>
         </is>
       </c>
-      <c r="ACM1" t="inlineStr">
+      <c r="ACM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP764</t>
         </is>
       </c>
-      <c r="ACN1" t="inlineStr">
+      <c r="ACN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP765</t>
         </is>
       </c>
-      <c r="ACO1" t="inlineStr">
+      <c r="ACO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP766</t>
         </is>
       </c>
-      <c r="ACP1" t="inlineStr">
+      <c r="ACP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP767</t>
         </is>
       </c>
-      <c r="ACQ1" t="inlineStr">
+      <c r="ACQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP768</t>
         </is>
       </c>
-      <c r="ACR1" t="inlineStr">
+      <c r="ACR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP769</t>
         </is>
       </c>
-      <c r="ACS1" t="inlineStr">
+      <c r="ACS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP770</t>
         </is>
       </c>
-      <c r="ACT1" t="inlineStr">
+      <c r="ACT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP771</t>
         </is>
       </c>
-      <c r="ACU1" t="inlineStr">
+      <c r="ACU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP772</t>
         </is>
       </c>
-      <c r="ACV1" t="inlineStr">
+      <c r="ACV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP773</t>
         </is>
       </c>
-      <c r="ACW1" t="inlineStr">
+      <c r="ACW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP774</t>
         </is>
       </c>
-      <c r="ACX1" t="inlineStr">
+      <c r="ACX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP775</t>
         </is>
       </c>
-      <c r="ACY1" t="inlineStr">
+      <c r="ACY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP776</t>
         </is>
       </c>
-      <c r="ACZ1" t="inlineStr">
+      <c r="ACZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP777</t>
         </is>
       </c>
-      <c r="ADA1" t="inlineStr">
+      <c r="ADA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP778</t>
         </is>
       </c>
-      <c r="ADB1" t="inlineStr">
+      <c r="ADB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP779</t>
         </is>
       </c>
-      <c r="ADC1" t="inlineStr">
+      <c r="ADC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP780</t>
         </is>
       </c>
-      <c r="ADD1" t="inlineStr">
+      <c r="ADD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP781</t>
         </is>
       </c>
-      <c r="ADE1" t="inlineStr">
+      <c r="ADE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP782</t>
         </is>
       </c>
-      <c r="ADF1" t="inlineStr">
+      <c r="ADF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP783</t>
         </is>
       </c>
-      <c r="ADG1" t="inlineStr">
+      <c r="ADG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP784</t>
         </is>
       </c>
-      <c r="ADH1" t="inlineStr">
+      <c r="ADH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP785</t>
         </is>
       </c>
-      <c r="ADI1" t="inlineStr">
+      <c r="ADI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP786</t>
         </is>
       </c>
-      <c r="ADJ1" t="inlineStr">
+      <c r="ADJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP787</t>
         </is>
       </c>
-      <c r="ADK1" t="inlineStr">
+      <c r="ADK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP788</t>
         </is>
       </c>
-      <c r="ADL1" t="inlineStr">
+      <c r="ADL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP789</t>
         </is>
       </c>
-      <c r="ADM1" t="inlineStr">
+      <c r="ADM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP790</t>
         </is>
       </c>
-      <c r="ADN1" t="inlineStr">
+      <c r="ADN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP791</t>
         </is>
       </c>
-      <c r="ADO1" t="inlineStr">
+      <c r="ADO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP792</t>
         </is>
       </c>
-      <c r="ADP1" t="inlineStr">
+      <c r="ADP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP793</t>
         </is>
       </c>
-      <c r="ADQ1" t="inlineStr">
+      <c r="ADQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP794</t>
         </is>
       </c>
-      <c r="ADR1" t="inlineStr">
+      <c r="ADR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP795</t>
         </is>
       </c>
-      <c r="ADS1" t="inlineStr">
+      <c r="ADS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP796</t>
         </is>
       </c>
-      <c r="ADT1" t="inlineStr">
+      <c r="ADT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP797</t>
         </is>
       </c>
-      <c r="ADU1" t="inlineStr">
+      <c r="ADU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP798</t>
         </is>
       </c>
-      <c r="ADV1" t="inlineStr">
+      <c r="ADV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP799</t>
         </is>
       </c>
-      <c r="ADW1" t="inlineStr">
+      <c r="ADW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP800</t>
         </is>
       </c>
-      <c r="ADX1" t="inlineStr">
+      <c r="ADX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP801</t>
         </is>
       </c>
-      <c r="ADY1" t="inlineStr">
+      <c r="ADY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP802</t>
         </is>
       </c>
-      <c r="ADZ1" t="inlineStr">
+      <c r="ADZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP803</t>
         </is>
       </c>
-      <c r="AEA1" t="inlineStr">
+      <c r="AEA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP804</t>
         </is>
       </c>
-      <c r="AEB1" t="inlineStr">
+      <c r="AEB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP805</t>
         </is>
       </c>
-      <c r="AEC1" t="inlineStr">
+      <c r="AEC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP806</t>
         </is>
       </c>
-      <c r="AED1" t="inlineStr">
+      <c r="AED1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP807</t>
         </is>
       </c>
-      <c r="AEE1" t="inlineStr">
+      <c r="AEE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP808</t>
         </is>
       </c>
-      <c r="AEF1" t="inlineStr">
+      <c r="AEF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP809</t>
         </is>
       </c>
-      <c r="AEG1" t="inlineStr">
+      <c r="AEG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP810</t>
         </is>
       </c>
-      <c r="AEH1" t="inlineStr">
+      <c r="AEH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP811</t>
         </is>
       </c>
-      <c r="AEI1" t="inlineStr">
+      <c r="AEI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP812</t>
         </is>
       </c>
-      <c r="AEJ1" t="inlineStr">
+      <c r="AEJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP813</t>
         </is>
       </c>
-      <c r="AEK1" t="inlineStr">
+      <c r="AEK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP814</t>
         </is>
       </c>
-      <c r="AEL1" t="inlineStr">
+      <c r="AEL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP815</t>
         </is>
       </c>
-      <c r="AEM1" t="inlineStr">
+      <c r="AEM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP816</t>
         </is>
       </c>
-      <c r="AEN1" t="inlineStr">
+      <c r="AEN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP817</t>
         </is>
       </c>
-      <c r="AEO1" t="inlineStr">
+      <c r="AEO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP818</t>
         </is>
       </c>
-      <c r="AEP1" t="inlineStr">
+      <c r="AEP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP819</t>
         </is>
       </c>
-      <c r="AEQ1" t="inlineStr">
+      <c r="AEQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP820</t>
         </is>
       </c>
-      <c r="AER1" t="inlineStr">
+      <c r="AER1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP821</t>
         </is>
       </c>
-      <c r="AES1" t="inlineStr">
+      <c r="AES1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP822</t>
         </is>
       </c>
-      <c r="AET1" t="inlineStr">
+      <c r="AET1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP823</t>
         </is>
       </c>
-      <c r="AEU1" t="inlineStr">
+      <c r="AEU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP824</t>
         </is>
       </c>
-      <c r="AEV1" t="inlineStr">
+      <c r="AEV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP825</t>
         </is>
       </c>
-      <c r="AEW1" t="inlineStr">
+      <c r="AEW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP826</t>
         </is>
       </c>
-      <c r="AEX1" t="inlineStr">
+      <c r="AEX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP827</t>
         </is>
       </c>
-      <c r="AEY1" t="inlineStr">
+      <c r="AEY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP828</t>
         </is>
       </c>
-      <c r="AEZ1" t="inlineStr">
+      <c r="AEZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP829</t>
         </is>
       </c>
-      <c r="AFA1" t="inlineStr">
+      <c r="AFA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP830</t>
         </is>
       </c>
-      <c r="AFB1" t="inlineStr">
+      <c r="AFB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP831</t>
         </is>
       </c>
-      <c r="AFC1" t="inlineStr">
+      <c r="AFC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP832</t>
         </is>
       </c>
-      <c r="AFD1" t="inlineStr">
+      <c r="AFD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP833</t>
         </is>
       </c>
-      <c r="AFE1" t="inlineStr">
+      <c r="AFE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP834</t>
         </is>
       </c>
-      <c r="AFF1" t="inlineStr">
+      <c r="AFF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP835</t>
         </is>
       </c>
-      <c r="AFG1" t="inlineStr">
+      <c r="AFG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP836</t>
         </is>
       </c>
-      <c r="AFH1" t="inlineStr">
+      <c r="AFH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP837</t>
         </is>
       </c>
-      <c r="AFI1" t="inlineStr">
+      <c r="AFI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP838</t>
         </is>
       </c>
-      <c r="AFJ1" t="inlineStr">
+      <c r="AFJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP839</t>
         </is>
       </c>
-      <c r="AFK1" t="inlineStr">
+      <c r="AFK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP840</t>
         </is>
       </c>
-      <c r="AFL1" t="inlineStr">
+      <c r="AFL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP841</t>
         </is>
       </c>
-      <c r="AFM1" t="inlineStr">
+      <c r="AFM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP842</t>
         </is>
       </c>
-      <c r="AFN1" t="inlineStr">
+      <c r="AFN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP843</t>
         </is>
       </c>
-      <c r="AFO1" t="inlineStr">
+      <c r="AFO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP844</t>
         </is>
       </c>
-      <c r="AFP1" t="inlineStr">
+      <c r="AFP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP845</t>
         </is>
       </c>
-      <c r="AFQ1" t="inlineStr">
+      <c r="AFQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP846</t>
         </is>
       </c>
-      <c r="AFR1" t="inlineStr">
+      <c r="AFR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP847</t>
         </is>
       </c>
-      <c r="AFS1" t="inlineStr">
+      <c r="AFS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP848</t>
         </is>
       </c>
-      <c r="AFT1" t="inlineStr">
+      <c r="AFT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP849</t>
         </is>
       </c>
-      <c r="AFU1" t="inlineStr">
+      <c r="AFU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP850</t>
         </is>
       </c>
-      <c r="AFV1" t="inlineStr">
+      <c r="AFV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP851</t>
         </is>
       </c>
-      <c r="AFW1" t="inlineStr">
+      <c r="AFW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP852</t>
         </is>
       </c>
-      <c r="AFX1" t="inlineStr">
+      <c r="AFX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP853</t>
         </is>
       </c>
-      <c r="AFY1" t="inlineStr">
+      <c r="AFY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP854</t>
         </is>
       </c>
-      <c r="AFZ1" t="inlineStr">
+      <c r="AFZ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP855</t>
         </is>
       </c>
-      <c r="AGA1" t="inlineStr">
+      <c r="AGA1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP856</t>
         </is>
       </c>
-      <c r="AGB1" t="inlineStr">
+      <c r="AGB1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP857</t>
         </is>
       </c>
-      <c r="AGC1" t="inlineStr">
+      <c r="AGC1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP858</t>
         </is>
       </c>
-      <c r="AGD1" t="inlineStr">
+      <c r="AGD1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP859</t>
         </is>
       </c>
-      <c r="AGE1" t="inlineStr">
+      <c r="AGE1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP860</t>
         </is>
       </c>
-      <c r="AGF1" t="inlineStr">
+      <c r="AGF1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP861</t>
         </is>
       </c>
-      <c r="AGG1" t="inlineStr">
+      <c r="AGG1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP862</t>
         </is>
       </c>
-      <c r="AGH1" t="inlineStr">
+      <c r="AGH1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP863</t>
         </is>
       </c>
-      <c r="AGI1" t="inlineStr">
+      <c r="AGI1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP864</t>
         </is>
       </c>
-      <c r="AGJ1" t="inlineStr">
+      <c r="AGJ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP865</t>
         </is>
       </c>
-      <c r="AGK1" t="inlineStr">
+      <c r="AGK1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP866</t>
         </is>
       </c>
-      <c r="AGL1" t="inlineStr">
+      <c r="AGL1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP867</t>
         </is>
       </c>
-      <c r="AGM1" t="inlineStr">
+      <c r="AGM1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP868</t>
         </is>
       </c>
-      <c r="AGN1" t="inlineStr">
+      <c r="AGN1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP869</t>
         </is>
       </c>
-      <c r="AGO1" t="inlineStr">
+      <c r="AGO1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP870</t>
         </is>
       </c>
-      <c r="AGP1" t="inlineStr">
+      <c r="AGP1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP871</t>
         </is>
       </c>
-      <c r="AGQ1" t="inlineStr">
+      <c r="AGQ1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP872</t>
         </is>
       </c>
-      <c r="AGR1" t="inlineStr">
+      <c r="AGR1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP873</t>
         </is>
       </c>
-      <c r="AGS1" t="inlineStr">
+      <c r="AGS1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP874</t>
         </is>
       </c>
-      <c r="AGT1" t="inlineStr">
+      <c r="AGT1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP875</t>
         </is>
       </c>
-      <c r="AGU1" t="inlineStr">
+      <c r="AGU1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP876</t>
         </is>
       </c>
-      <c r="AGV1" t="inlineStr">
+      <c r="AGV1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP877</t>
         </is>
       </c>
-      <c r="AGW1" t="inlineStr">
+      <c r="AGW1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP878</t>
         </is>
       </c>
-      <c r="AGX1" t="inlineStr">
+      <c r="AGX1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP879</t>
         </is>
       </c>
-      <c r="AGY1" t="inlineStr">
+      <c r="AGY1" s="1" t="inlineStr">
         <is>
           <t>PubchemFP880</t>
         </is>
@@ -18999,7 +19011,7 @@
       </c>
       <c r="GC5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="GD5" t="inlineStr">
@@ -19089,7 +19101,7 @@
       </c>
       <c r="GU5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="GV5" t="inlineStr">
@@ -19364,7 +19376,7 @@
       </c>
       <c r="IX5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="IY5" t="inlineStr">
